--- a/02_加值成品/八上/八上5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-1 溫度與溫度計　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上5-1 溫度與溫度計　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>溫度表示物體的什麼？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>運動劇烈程度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>熱脹冷縮</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>冷熱程度</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>溫度上升</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>量度</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>攝氏溫標水的冰點是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>0℃</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>待熱平衡</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>溫度上升</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>標準</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>攝氏溫標水的沸點是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>需與身體達熱平衡</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0℃</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>100℃</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>1atm</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>溫度計利用液體什麼性質？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>冰點</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>熱脹冷縮</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>一桶</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>體積變化</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>溫度反映粒子的？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>運動劇烈程度</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>越劇烈</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>越熱越快</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>測較高溫常用哪種溫度計？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>水銀溫度計</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>℉</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>沸點高</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>溫度計要與待測物達到？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>降低</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>越劇烈</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>熱平衡</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>接觸</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>同溫</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>攝氏溫標符號是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>待熱平衡</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>℃</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>度C</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>冷熱程度用什麼量化？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>熱脹冷縮</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>水銀溫度計</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>溫度</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>越劇烈</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>量度</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>水在1大氣壓沸騰溫度是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>沸點降低溫度不足</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>熱脹冷縮</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>100℃</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>溫度上升</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>沸點</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-1 溫度與溫度計　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上5-1 溫度與溫度計　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>溫度越高粒子運動如何？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>熱平衡</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>越劇烈</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>動能大</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>酒精溫度計適合測？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>運動劇烈程度</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>較低溫</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>酒精沸點低</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>為何溫度計要等一下再讀？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>待熱平衡</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>溫度上升</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>較低溫</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>溫度與熱量是同一件事嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>接觸</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>水銀溫度計</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>冷熱程度vs能量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>紅外線溫度計測溫不需？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>接觸</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>運動劇烈程度</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>非接觸</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>水的沸點在高山會？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>降低</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>運動劇烈程度</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>氣壓低</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>溫度計液柱上升代表？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>越劇烈</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>溫度上升</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>熱脹冷縮</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>高溫往低溫</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>受熱膨脹</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>華氏溫標符號？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>溫度上升</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>℉</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>度F</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>攝氏0度相當於水的？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>溫度上升</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>熱平衡</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>冰點</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>標準</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>溫度計插入熱水中液柱會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>熱脹冷縮</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>℉</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>較低溫</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>熱脹</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-1 溫度與溫度計　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上5-1 溫度與溫度計　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何說溫度不是熱量？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>需與身體達熱平衡</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>防水銀回流讀取穩定</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>溫度是冷熱程度,熱量是能量傳遞</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>沸點降低溫度不足</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>一杯與一桶同溫水,何者熱量多？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>較低溫</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>一桶</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>℉</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>量多能量多</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>溫度計測溫時本身吸熱會影響嗎？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>需與身體達熱平衡</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>桶,質量大含熱量多</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>微量,小體積影響小</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>防水銀回流讀取穩定</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>誤差</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>高山煮蛋不易熟因為？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>桶,質量大含熱量多</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>防水銀回流讀取穩定</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>微量,小體積影響小</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>沸點降低溫度不足</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>氣壓</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>為何體溫計有縮口設計？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>沸點降低溫度不足</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>防水銀回流讀取穩定</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>溫度是冷熱程度,熱量是能量傳遞</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>需與身體達熱平衡</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>兩物接觸熱由何處往何處？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>水銀溫度計</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>高溫往低溫</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>熱流方向</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>達熱平衡時兩物溫度？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>熱平衡</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>水銀溫度計</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>運動劇烈程度</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>溫度計刻度均勻假設液體？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>冷熱程度</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>待熱平衡</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>熱平衡</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>均勻膨脹</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>線性</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何量體溫要等數秒才讀取？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>溫度是冷熱程度,熱量是能量傳遞</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>沸點降低溫度不足</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>微量,小體積影響小</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>需與身體達熱平衡</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>熱平衡</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>同溫的一杯與一桶水熱量誰多?為何</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>需與身體達熱平衡</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>沸點降低溫度不足</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>溫度是冷熱程度,熱量是能量傳遞</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>桶,質量大含熱量多</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>熱量</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>量度</t>
+          <t>量度：溫度是用來客觀量化物體冷熱程度的物理量</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>標準</t>
+          <t>標準：攝氏溫標把水結冰的溫度定為0度，這是攝氏溫標的基準點之一</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>1atm</t>
+          <t>1atm：在一大氣壓下，攝氏溫標把水沸騰的溫度定為100℃</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>體積變化</t>
+          <t>體積變化：溫度計內的液體受熱時體積膨脹、變冷時體積收縮，靠這種熱脹冷縮的特性來指示溫度</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>越熱越快</t>
+          <t>越熱越快：溫度其實反映了物質內部粒子運動的劇烈程度，溫度越高，粒子運動得越快、越劇烈</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>沸點高</t>
+          <t>沸點高：水銀的沸點很高，適合用來測量較高的溫度而不會因為溫度計本身液體先沸騰而失效</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>同溫</t>
+          <t>同溫：溫度計必須和待測物體充分接觸、達到相同溫度(熱平衡)後，讀數才會準確反映待測物的真實溫度</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>度C</t>
+          <t>度C：攝氏溫標的英文是Celsius，符號寫成℃</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>量度</t>
+          <t>量度：溫度是用來客觀量化物體冷熱程度的物理量</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>沸點</t>
+          <t>沸點：在標準的1大氣壓下，水加熱到100℃就會沸騰，這個溫度稱為水的沸點</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>動能大</t>
+          <t>動能大：溫度越高，物質內部粒子的平均動能越大，運動也越劇烈</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>酒精沸點低</t>
+          <t>酒精沸點低：酒精的沸點比水銀低很多，適合用來測量較低的溫度，若測高溫酒精可能先沸騰而失效</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：溫度計剛接觸待測物時溫度還沒完全同步，需要等待一段時間讓兩者達到熱平衡，這時讀到的溫度才穩定準確</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>冷熱程度vs能量</t>
+          <t>冷熱程度vs能量：溫度只是表示冷熱程度的物理量，熱量則是能量傳遞的多寡，兩者概念不同，不能混為一談</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>非接觸</t>
+          <t>非接觸：紅外線溫度計靠偵測物體發出的紅外線輻射來判斷溫度，不需要直接接觸待測物體</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>氣壓低</t>
+          <t>氣壓低：高山上氣壓比平地低，水不需要加熱到100度就能沸騰，所以沸點會降低</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>受熱膨脹</t>
+          <t>受熱膨脹：溫度計內的液體受熱後體積膨脹、沿著細管往上升，液柱上升代表溫度升高</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>度F</t>
+          <t>度F：華氏溫標的英文是Fahrenheit，符號寫成℉</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>標準</t>
+          <t>標準：攝氏溫標把水結冰的溫度定為0度，這個溫度稱為冰點，是攝氏溫標的基準點之一</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>熱脹</t>
+          <t>熱脹：溫度計內的液體受熱後體積膨脹，會沿著細管往上升，液柱高度上升代表溫度升高</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>觀念：溫度只代表冷熱程度這個狀態，熱量則是物體間傳遞的能量多寡，兩者是不同的物理概念，不可混淆</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>量多能量多</t>
+          <t>量多能量多：溫度只代表冷熱程度，熱量還與質量有關，質量越大含有的熱量越多，所以同溫度下一桶水比一杯水含有更多熱量</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>誤差</t>
+          <t>誤差：溫度計接觸待測物時多少會吸收一點熱量，但因為溫度計體積很小，吸收的熱量相對待測物的熱量微不足道，造成的誤差通常可以忽略</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>氣壓</t>
+          <t>氣壓：高山氣壓低使水的沸點降低，水沸騰時的溫度不到100℃，蛋在較低溫度下煮沸的水中不容易煮熟</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>構造</t>
+          <t>構造：體溫計在近球部處有一段細縮的設計，水銀受熱膨脹後能通過細縮口往上升，但離開身體降溫後水銀不易自動回流，方便醫護人員穩定讀取剛才量到的體溫</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>熱流方向</t>
+          <t>熱流方向：兩個溫度不同的物體接觸時，熱量會自然地從溫度較高的物體流向溫度較低的物體，直到達到熱平衡</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：兩物體達到熱平衡狀態時，彼此之間不再有淨熱量流動，此時兩者的溫度相同</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>線性</t>
+          <t>線性：溫度計上的刻度是均勻分布的，這是假設液體受熱時體積會隨溫度呈線性(均勻)膨脹而設計的</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>熱平衡</t>
+          <t>熱平衡：溫度計剛接觸身體時溫度還沒完全同步，需要等待一段時間讓溫度計與身體達到熱平衡，這時讀到的溫度才準確</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>熱量</t>
+          <t>熱量：溫度只代表冷熱程度，熱量還與質量有關，質量越大含有的熱量越多，所以同溫度下一桶水比一杯水含有更多熱量</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-1_三種難度測驗卷.xlsx
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>待熱平衡</t>
+          <t>冰點</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>溫度上升</t>
+          <t>一桶</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>冷熱程度</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -643,17 +643,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>冷熱程度</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>需與身體達熱平衡</t>
+          <t>溫度上升</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>0℃</t>
+          <t>越劇烈</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>℉</t>
+          <t>高溫往低溫</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>℃</t>
+          <t>較低溫</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>冷熱程度</t>
+          <t>熱平衡</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -803,22 +803,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>高溫往低溫</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>熱脹冷縮</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>熱平衡</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>降低</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>越劇烈</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>熱平衡</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>接觸</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>水銀溫度計</t>
+          <t>熱平衡</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>越劇烈</t>
+          <t>降低</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>沸點降低溫度不足</t>
+          <t>待熱平衡</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>溫度上升</t>
+          <t>冷熱程度</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>溫度上升</t>
+          <t>均勻膨脹</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>冷熱程度</t>
+          <t>℉</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>越劇烈</t>
+          <t>℉</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>熱脹冷縮</t>
+          <t>一桶</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>高溫往低溫</t>
+          <t>℃</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1399,22 +1399,22 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>均勻膨脹</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>熱脹冷縮</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>℉</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>上升</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>較低溫</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
